--- a/bgf_frozen_picking_template.xlsx
+++ b/bgf_frozen_picking_template.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78271971-5520-4072-99FC-81F1E6B19192}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33930" yWindow="0" windowWidth="22725" windowHeight="15420" tabRatio="905" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33930" yWindow="0" windowWidth="22725" windowHeight="15420" tabRatio="905" firstSheet="0" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="★참조은 피벗( 냉동)3438600" sheetId="1715" r:id="rId4"/>

--- a/bgf_frozen_picking_template.xlsx
+++ b/bgf_frozen_picking_template.xlsx
@@ -405,8 +405,7 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>김해</t>
-    <phoneticPr fontId="13" type="noConversion"/>
+    <t xml:space="preserve">기장</t>
   </si>
   <si>
     <t>김해2</t>
@@ -889,7 +888,7 @@
     <t>극동로지스</t>
   </si>
   <si>
-    <t>김해물류</t>
+    <t xml:space="preserve">BGF로지스기장</t>
   </si>
   <si>
     <t>BGF로지스부산</t>
@@ -1041,7 +1040,7 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>경남(김해)합계</t>
+    <t>경남(기장)합계</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
@@ -5624,11 +5623,11 @@
   <mergeCells count="7">
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -6556,11 +6555,11 @@
   <mergeCells count="7">
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -8963,11 +8962,11 @@
   <mergeCells count="7">
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -9975,11 +9974,11 @@
   <mergeCells count="7">
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -10907,11 +10906,11 @@
   <mergeCells count="7">
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -11919,11 +11918,11 @@
   <mergeCells count="7">
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -12933,11 +12932,11 @@
   <mergeCells count="7">
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -13865,11 +13864,11 @@
   <mergeCells count="7">
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -14797,11 +14796,11 @@
   <mergeCells count="7">
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -16772,11 +16771,11 @@
   <mergeCells count="7">
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -20237,12 +20236,12 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -21172,12 +21171,12 @@
   </sortState>
   <mergeCells count="7">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A34:F34"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -23143,11 +23142,11 @@
   <mergeCells count="7">
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -24075,11 +24074,11 @@
   <mergeCells count="7">
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B2:F2"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A29:F29"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <phoneticPr fontId="13" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
